--- a/hasil/Non-CLAHE/Run2/hasil_metrik.xlsx
+++ b/hasil/Non-CLAHE/Run2/hasil_metrik.xlsx
@@ -482,28 +482,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8222222222222222</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.8235294117647058</v>
       </c>
     </row>
     <row r="3">
@@ -516,25 +516,25 @@
         <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H3" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7407407407407408</v>
       </c>
     </row>
     <row r="4">
@@ -547,25 +547,25 @@
         <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9111111111111111</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="H4" t="n">
         <v>0.8666666666666667</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.896551724137931</v>
       </c>
     </row>
     <row r="6">
@@ -577,7 +577,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.7555555555555555</v>
+        <v>0.8222222222222222</v>
       </c>
     </row>
     <row r="9">
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -620,13 +620,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
